--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,32 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>tech, ai, news, shorts, cloudflare, webdev, api, search, developers, privacy, programming, innovation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-06 05:21:25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Is Common Lisp REALLY the BEST Programming Language? 🤯 #CommonLisp #Programming #TechNews #Shorts</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Hold up, programmers! Is Common Lisp, yes, *that* Lisp, now the best programming language? A recent buzz suggests this ancient language is making a powerful comeback. Why the sudden hype?
+Common Lisp offers unmatched extensibility through its legendary macro system. Imagine writing code that writes code – that's Lisp power! Plus, its interactive REPL lets you build and test on the fly, making development incredibly dynamic and iterative.
+It's not just for academics anymore. Lisp is behind powerful systems, known for its flexibility and ability to tackle complex problems where other languages might struggle. It truly lets you shape the language to your problem, not the other way around.
+So, while it might not be mainstream, its unique approach to metaprogramming and dynamic environments is turning heads. Are we witnessing a Lisp renaissance?
+What do you think? Is Common Lisp truly the GOAT? Let me know in the comments!</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>tech, programming, lisp, commonlisp, softwaredevelopment, coders, programminglanguages, dev, hacker, shorts, news, codinglife</t>
         </is>
       </c>
     </row>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,6 +511,28 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-06 05:39:36</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Common Lisp: The *BEST* Programming Language Now?! 🤯 #TechNews #Programming</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Hold up, tech fam! A bold claim is shaking the programming world: 'Why Common Lisp is now the best programming language!' What?! This isn't your grandpa's Lisp. The internet is buzzing, and for good reason. Imagine a language where you practically write the language itself with macros. Yes, meta-programming on steroids! Common Lisp offers incredible interactive development, unmatched stability, and a rich, powerful ecosystem that's been proven for decades. Developers are rediscovering its unique strengths for AI, complex systems, and rapid prototyping. Is it really the new king? Dive into the discussion. Link to the full article and the Hacker News debate in the description! What are YOUR thoughts? Let us know!</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>tech, programming, lisp, commonlisp, coding, softwaredevelopment, programminglanguage, technews, shorts, developer, hacker news</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,6 +533,30 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:23:51</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Common Lisp: The 'BEST' Programming Language RIGHT NOW?! 🤯 #Lisp #Programming #TechNews #Shorts</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hold up! Common Lisp... the BEST programming language RIGHT NOW? Yeah, you heard that right! A recent headline is sparking a massive debate, making some bold claims about this classic language. But why Lisp? Isn't it... old school?
+Well, Lisp isn't just old; it's *powerful*. We're talking mind-bending macros that let you extend the language itself, and a legendary REPL for truly interactive development, giving you instant feedback. This isn't just theoretical; its unparalleled flexibility and expressive power influenced countless modern languages.
+From AI pioneers to cutting-edge embedded systems, Lisp's principles are everywhere. Is it *actually* the definitive 'best'? That's subjective, of course! But its unique paradigm offers elegant solutions modern languages often struggle to replicate. Ready to rethink your coding stack? Dive into the full article and join the discussion. Link in bio!</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CommonLisp, Lisp, ProgrammingLanguage, TechNews, Coding, Developer, SoftwareDevelopment, Shorts, Tech, HackerNews, AI, FunctionalProgramming</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,6 +533,28 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:03:27</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Is Common Lisp The BEST Programming Language?! 🚀 #TechNews #Programming #Lisp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hold up, tech enthusiasts! A bold claim is shaking the internet: Common Lisp is now the best programming language. Really? Let's dive in! Yep, we're talking about Lisp, a language from the 1950s! But don't dismiss it. Recent discussions highlight its incredible power, especially for complex systems and AI research. What makes it 'best'? Common Lisp offers unparalleled metaprogramming capabilities. Imagine a language that can literally write and modify itself while it's running! Then there's its incredible stability and flexibility. Programs written decades ago often still compile and run perfectly, a rare feat in the fast-paced tech world. While it might seem niche, Lisp powers critical systems and is making a quiet comeback in AI, scientific computing, and advanced software development. So, is Common Lisp the *best*? Its unique strengths are undeniable, but it's not for everyone. What do YOU think? Let us know in the comments!</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>tech, programming, commonlisp, lisp, developers, coding, softwaredevelopment, shorts, techtalk, ai, news</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,28 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:52:31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Beam: Reflection.ai's 501B Open-Weight AI Model JUST DROPPED! #TechNews #AI #OpenSource</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Whoa, tech heads, buckle up! A monumental AI announcement just dropped: Meet Beam, Reflection.ai's game-changing new model! This isn't just *another* large language model; we're talking about a colossal 501 BILLION parameter, open-weight powerhouse! That's right – five hundred and one billion parameters, *openly released* to the community! Reflection.ai is shaking up the AI landscape, giving researchers, startups, and developers unprecedented access to a model of this incredible scale. Think about the possibilities: from pushing boundaries in natural language processing to enabling entirely new, mind-bending applications. Beam is set to ignite a massive wave of innovation, fostering collaboration and accelerating progress. This is a HUGE win for open-source AI, directly challenging proprietary giants and democratizing cutting-edge capabilities. What incredible innovations will *you* unlock with Beam? The future of AI just got a whole lot more open and exciting. Dive deeper – links are in the description!</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>tech, ai, news, shorts, beam, reflectionai, opensource, llm, machinelearning, artificialintelligence, techshorts, innovation, futureofai, deeplearning, developer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,6 +579,28 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:45:12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Francis Halzen Wins Nobel Physics 2026! 🏆 #NobelPrize #Physics #IceCube #TechNews</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Breaking News, science fans! The Nobel Prize in Physics 2026 goes to Professor Francis Halzen! He's the genius behind the IceCube Neutrino Observatory. Halzen's team detects high-energy cosmic neutrinos – 'ghost particles' from exploding stars and black holes! This revolutionary work gives us a new way to literally 'see' the universe's most extreme events. It's a monumental leap for astrophysics, unraveling cosmic origins. What does this Nobel mean for our future understanding of space? Tell us in the comments! Congrats, Professor Halzen!</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>tech, news, shorts, nobelprize, physics, francishalzen, icecube, neutrino, astrophysics, science, space, cosmos, innovation, discovery, 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,6 +601,28 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:35:16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mistral Large 4 Just Dropped! 🤯 AI Just Got SMARTER! #MistralAI #TechNews #AINews #Shorts</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tech world, buckle up! Mistral AI just made a massive move, unleashing 'Mistral Large 4' – their most advanced and powerful language model to date! This isn't just another update; it's a significant leap forward, designed to redefine what's possible with generative AI. Mistral Large 4 is engineered for peak performance, boasting impressive reasoning abilities and a deep understanding of complex tasks. It's stepping onto the global stage, ready to challenge even the biggest names in the LLM space. Imagine faster development, more accurate results, and groundbreaking AI applications across industries. This new model promises unparalleled efficiency and cutting-edge capabilities. It’s set to empower developers and transform how we interact with intelligent systems. The future of AI is evolving fast, and Mistral Large 4 is leading the charge. What incredible things do you think this new model will enable? Let us know in the comments! Stay ahead of the curve!</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>tech, ai, news, shorts, MistralAI, LLM, ArtificialIntelligence, ML, GenAI, Innovation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,6 +623,28 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:32:10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GitHub Glitch! 🚨 Devs, Did You Notice? #GitHubDown #TechNews #DevLife</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hey devs, quick heads-up! GitHub just had a significant incident. If you faced issues with your Git operations, Pull Requests, or even GitHub Actions, you weren't alone. For a period, many developers experienced disruptions across these critical services. GitHub's status page confirmed the problem, affecting millions of projects globally. While they worked quickly to address it, it was a stark reminder of our reliance on these platforms. Always check GitHub's status page during outages! What's your backup plan when GitHub goes down? Let us know in the comments! Stay updated with the latest tech news right here.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>tech, news, github, developers, programming, coding, devops, shorts, outage, git, pullrequests, githubactions, incident</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,66 +582,110 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06 10:45:12</t>
+          <t>2026-10-07 21:35:54</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Francis Halzen Wins Nobel Physics 2026! 🏆 #NobelPrize #Physics #IceCube #TechNews</t>
+          <t>GitHub Down? గిట్ హబ్ లో సమస్యలు! 🤯 #GitHub #TechNewsTelugu #TeluguShorts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Breaking News, science fans! The Nobel Prize in Physics 2026 goes to Professor Francis Halzen! He's the genius behind the IceCube Neutrino Observatory. Halzen's team detects high-energy cosmic neutrinos – 'ghost particles' from exploding stars and black holes! This revolutionary work gives us a new way to literally 'see' the universe's most extreme events. It's a monumental leap for astrophysics, unraveling cosmic origins. What does this Nobel mean for our future understanding of space? Tell us in the comments! Congrats, Professor Halzen!</t>
+          <t>హేయ్ టెక్ ప్రియులారా! ఇప్పుడే ఒక హాట్ న్యూస్ తో మీ ముందుకు వచ్చాను. మీరు గిట్ హబ్ వాడుతున్నారా? అయితే మీకు నిన్నటి నుంచి చిన్నపాటి షాక్ తగిలి ఉండొచ్చు. అవును, గిట్ హబ్ లో కొన్ని సమస్యలు తలెత్తాయి. గిట్ ఆపరేషన్స్, పుల్ రిక్వెస్ట్‌లు, గిట్ హబ్ యాక్షన్స్ వంటి ముఖ్యమైన ఫీచర్లు పనిచేయడం లేదని చాలా మంది డెవలపర్లు కంప్లైంట్ చేశారు. దీని వల్ల ప్రాజెక్ట్ డెవలప్‌మెంట్‌లో కాస్త బ్రేక్ వచ్చింది. కానీ వర్రీ అవ్వకండి! గిట్ హబ్ టీమ్ ఈ సమస్యను గుర్తించి, వేగంగా పరిష్కరించడానికి పని చేస్తుంది. త్వరలోనే అంతా నార్మల్ అవుతుందని ఆశిద్దాం. మరిన్ని టెక్ అప్‌డేట్స్ కోసం మన ఛానెల్‌ని సబ్‌స్క్రైబ్ చేసుకోండి! మీరేమైనా సమస్యలు ఎదుర్కొన్నారా? కామెంట్స్ లో చెప్పండి!</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>tech, news, shorts, nobelprize, physics, francishalzen, icecube, neutrino, astrophysics, science, space, cosmos, innovation, discovery, 2026</t>
+          <t>tech, telugu, ai, news, shorts, github, coding, developers, git</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06 13:35:16</t>
+          <t>2026-10-07 22:52:51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mistral Large 4 Just Dropped! 🤯 AI Just Got SMARTER! #MistralAI #TechNews #AINews #Shorts</t>
+          <t>వీసా, మాస్టర్‌కార్డ్, బ్యాంకులపై దావా! 🚨 ఏంటి కథ? #TechNewsTelugu #VisaMastercard</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tech world, buckle up! Mistral AI just made a massive move, unleashing 'Mistral Large 4' – their most advanced and powerful language model to date! This isn't just another update; it's a significant leap forward, designed to redefine what's possible with generative AI. Mistral Large 4 is engineered for peak performance, boasting impressive reasoning abilities and a deep understanding of complex tasks. It's stepping onto the global stage, ready to challenge even the biggest names in the LLM space. Imagine faster development, more accurate results, and groundbreaking AI applications across industries. This new model promises unparalleled efficiency and cutting-edge capabilities. It’s set to empower developers and transform how we interact with intelligent systems. The future of AI is evolving fast, and Mistral Large 4 is leading the charge. What incredible things do you think this new model will enable? Let us know in the comments! Stay ahead of the curve!</t>
+          <t>నమస్తే టెక్ ప్రియులారా! ఆర్థిక ప్రపంచంలో ఇప్పుడు పెద్ద అలజడి! వీసా, మాస్టర్‌కార్డ్, ఇంకా కొన్ని ప్రముఖ బ్యాంకులు భారీ లీగల్ చిక్కుల్లో పడ్డాయి. అవును, మీరు విన్నది నిజమే! క్రెడిట్ కార్డ్ లావాదేవీలపై వ్యాపారుల నుండి 'అన్యాయమైన' ఫీజులు వసూలు చేస్తున్నాయంటూ వాటిపై కొత్తగా దావా వేయబడింది. ఈ 'యాంటీకాంపిటీటివ్' ఫీజుల వల్ల వ్యాపారాలు కార్డు పేమెంట్స్ ప్రాసెస్ చేయడానికి భారీగా ఖర్చు చేయాల్సి వస్తుంది. చివరికి, ఈ భారం వినియోగదారులైన మనపైనే పడుతుందని నిపుణులు అంటున్నారు. మరి ఈ కేసు ఫలితం ఏమవుతుంది? బ్యాంకింగ్ రంగంలో ఎలాంటి మార్పులు వస్తాయో చూడాలి. ఈ విషయంపై మీ అభిప్రాయం ఏంటి? కామెంట్ల రూపంలో మాకు తెలియజేయండి! మన ఛానెల్‌ని సబ్స్క్రైబ్ చేసుకోవడం మర్చిపోకండి!</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>tech, ai, news, shorts, MistralAI, LLM, ArtificialIntelligence, ML, GenAI, Innovation</t>
+          <t>tech, telugu, news, shorts, visa, mastercard, banks, lawsuit, financialnews, techintelugu, business, consumerrights</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07 15:32:10</t>
+          <t>2026-10-08 07:16:48</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GitHub Glitch! 🚨 Devs, Did You Notice? #GitHubDown #TechNews #DevLife</t>
+          <t>సరికొత్త క్లాడ్ హైకు 5.5 AI | Anthropic కొత్త మోడల్ వచ్చేసింది! 🚀 #ClaudeHaiku #AI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hey devs, quick heads-up! GitHub just had a significant incident. If you faced issues with your Git operations, Pull Requests, or even GitHub Actions, you weren't alone. For a period, many developers experienced disruptions across these critical services. GitHub's status page confirmed the problem, affecting millions of projects globally. While they worked quickly to address it, it was a stark reminder of our reliance on these platforms. Always check GitHub's status page during outages! What's your backup plan when GitHub goes down? Let us know in the comments! Stay updated with the latest tech news right here.</t>
+          <t>హే టెక్ ప్రియులారా! AI ప్రపంచంలో మరో సంచలనానికి స్వాగతం! Anthropic నుండి సరికొత్త Claude Haiku 5.5 AI మోడల్ వచ్చేసింది. ఇది మునుపటి వెర్షన్ల కంటే చాలా వేగంగా, తక్కువ ఖర్చుతో పనిచేస్తుంది. మీ రోజువారీ AI పనులని మరింత సులభతరం చేస్తుంది. డెవలపర్స్, బిజినెస్ ల కోసం ఇది ఒక గేమ్ చేంజర్. క్లిష్టమైన డేటా అనాలిసిస్, కస్టమర్ సపోర్ట్, కోడింగ్ అసిస్టెన్స్ లాంటి వాటికి పర్ఫెక్ట్. రియల్ టైమ్ ప్రాసెసింగ్ సామర్థ్యంతో, Haiku 5.5 మీ ఉత్పాదకతను అమాంతం పెంచుతుంది. ఇది నిజంగా వేగం, సామర్థ్యం యొక్క అద్భుతమైన కలయిక. మీ ప్రాజెక్ట్స్ మరింత వేగంగా పూర్తవుతాయి. మరిన్ని టెక్ అప్డేట్స్ కోసం మా ఛానెల్ ని సబ్స్క్రైబ్ చేసుకోండి! Claude Haiku 5.5 గురించి మీరేమనుకుంటున్నారు? కామెంట్స్ లో చెప్పండి! తెలుగులో మరిన్ని టెక్ న్యూస్ కోసం చూస్తూ ఉండండి!</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>tech, news, github, developers, programming, coding, devops, shorts, outage, git, pullrequests, githubactions, incident</t>
+          <t>tech, telugu, ai, news, shorts, ClaudeHaiku, Anthropic, AIModel, TechNews, TeluguTech, ArtificialIntelligence, AIUpdate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-08 07:33:09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Claude Haiku 5.5: వేగవంతమైన, చవకైన AI వచ్చేసింది! 🚀 #AI #TeluguTech</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>హేయ్ టెక్ లవర్స్! AI ప్రపంచంలో మరో సంచలనం! Anthropic నుండి సరికొత్త Claude Haiku 5.5 వచ్చేసింది! గతంలో కంటే ఇంకా వేగంగా, చాలా తక్కువ ఖర్చుతో పనిచేసే ఈ AI మోడల్, చిన్న వ్యాపారాలకు, డెవలపర్‌లకు నిజంగా గేమ్-ఛేంజర్. కోడింగ్, కంటెంట్ క్రియేషన్, డేటా అనాలిసిస్.. ఇలా ఎన్నో పనులను క్షణాల్లో చేసేస్తుంది. ఇకపై AI శక్తి అందరికీ అందుబాటులోకి వస్తుంది. క్లాడ్ హైకు 5.5 సామర్థ్యాన్ని చూసి తీరాల్సిందే! మరిన్ని ఆసక్తికరమైన టెక్ అప్‌డేట్‌ల కోసం వెంటనే మన ఛానెల్‌ని సబ్‌స్క్రైబ్ చేసుకోండి!</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, claude haiku, anthropic, artificial intelligence, ai models, telugu tech news, fast ai, cost effective ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-08 07:42:54</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Claude Haiku 5.5: కొత్త AI వచ్చేసింది! 🚀🔥 | Anthropic AI Update #TeluguTech</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ఒక అదిరిపోయే AI అప్డేట్! Anthropic నుండి సరికొత్త Claude Haiku 5.5 వచ్చేసింది! మీరు నమ్మలేరు... ఇది మునుపటి కంటే రెండు రెట్లు వేగంగా పనిచేస్తుంది! అవును, రెండంతలు ఫాస్ట్! అంతేకాదు, ఇది మరింత స్మార్ట్, తక్కువ ధరలో ఎక్కువ పని చేస్తుంది. కోడింగ్, లాజిక్, డిఫరెంట్ భాషల్లో కూడా అద్భుతమైన పర్ఫార్మెన్స్! ఇది మీ AI ప్రాజెక్టులకు బెస్ట్ ఆప్షన్ కావచ్చు. మరింత సమాచారం కోసం Anthropic వెబ్సైట్ చూడండి! AI ప్రపంచంలో ఇది ఒక గేమ్ ఛేంజర్! మిస్ అవ్వకండి!</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, claudehaiku, anthropic, aitools, telugutech, latestai</t>
         </is>
       </c>
     </row>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,6 +689,28 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-08 02:29:04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Claude Haiku 5.5: AIలో కొత్త విప్లవం! 🔥 #AI #TeluguTech #ClaudeHaiku</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>నమస్తే టెక్ ప్రియులారా! సరికొత్త AI అప్‌డేట్ కోసం ఎదురు చూస్తున్నారా? అయితే వినండి! Anthropic నుండి "Claude Haiku 5.5" వచ్చేసింది! ఇది కేవలం అప్‌డేట్ కాదు, ఒక విప్లవం! ఈ కొత్త వెర్షన్ మునుపటి కంటే చాలా వేగంగా, చాలా తెలివిగా పనిచేస్తుంది. మీ పనులను చిటికెలో పూర్తి చేస్తుంది. ప్రత్యేకంగా, చిన్నచిన్న పనులకు, కస్టమర్ సపోర్ట్‌కి ఇది పర్‌ఫెక్ట్. తక్కువ సమయంలో ఎక్కువ అవుట్‌పుట్ అందిస్తుంది. దీని సామర్థ్యం అద్భుతం. డేటా అనాలసిస్ అయినా, కంటెంట్ జనరేషన్ అయినా, Haiku 5.5 మీ నమ్మకమైన AI పార్ట్‌నర్ అవుతుంది. పైగా, ఇది చాలా ఖర్చు తక్కువ! స్పీడ్, తెలివితేటలు, మరియు తక్కువ ఖర్చు - అన్నీ ఒకే చోట! టెక్ ప్రపంచంలో సరికొత్త సంచలనం ఈ Claude Haiku 5.5. మరిన్ని టెక్ అప్‌డేట్స్ కోసం మా ఛానెల్‌ని సబ్స్క్రైబ్ చేసుకోండి!</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, claudehaiku, anthropic, artificialintelligence, techupdates, telugunews</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,6 +711,32 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:09:40</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DVD మెనూల అందం: పాత జ్ఞాపకాలు! 🎨 #TechNostalgia #DVDMenus</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>హేయ్ టెక్ లవర్స్! ఈ రోజు ఒక సూపర్ టెక్ న్యూస్ చూద్దాం! మనం ఇప్పుడు నెట్‌ఫ్లిక్స్, ప్రైమ్ అని స్ట్రీమింగ్ యుగంలో ఉన్నాం కదా? కానీ ఒకప్పుడు DVD లు గుర్తుందా? వాటి మెనూలు... అద్భుతం కదా!
+అవును, ఒకప్పుడు డివిడి మెనూలు కేవలం సినిమాలు ప్లే చేయడానికే కాదు, ఒక కళాఖండంలా ఉండేవి. ఆ యానిమేషన్స్, ఆ బ్యాక్‌గ్రౌండ్ మ్యూజిక్, ఆ డీటెయిల్స్... వావ్! ఒక్కో సినిమాకి ఒక్కో థీమ్‌తో ఎంత క్రియేటివిటీ చూపించేవాళ్లో!
+ప్రతీ మెనూని డిజైన్ చేయడానికి గ్రాఫిక్ డిజైనర్లు, యానిమేటర్లు ఎంత కష్టపడ్డారో! ఇప్పుడున్న సింపుల్ యూఐ లకు అవి అసలైన కళను గుర్తుచేస్తాయి. ఒక విధంగా, ఆ మెనూలు మనల్ని సినిమాలోకి తీసుకెళ్లే మొదటి అడుగు.
+ఇప్పుడు మనం అంతా ఫాస్ట్ ఫార్వార్డ్ చేసేస్తాం. కానీ ఆ డివిడి మెనూలు కొన్నిసార్లు సినిమా కంటే ఎక్కువ ఇంప్రెస్ చేసేవి! అవి మన చిన్ననాటి జ్ఞాపకాలను, ఆ టెక్నాలజీ అందాన్ని గుర్తుచేస్తాయి.
+ఈ డివిడి మెనూల డిజైన్ గురించి మీరు ఏమనుకుంటున్నారు? మీ ఫేవరెట్ మెనూ ఏంటి? కామెంట్ చేయండి! పాత టెక్ అందాలను మర్చిపోకండి!</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, dvd, vintage tech, nostalgia, tech news telugu, dvd menus, retro tech</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,6 +737,28 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:55:05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Deno Cloudflare లోకి! టెక్ ప్రపంచంలో సంచలనం! #Deno #Cloudflare #TechNewsTelugu</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>హాయ్ టెక్ ఫ్రెండ్స్! ఈరోజు ఒక అదిరిపోయే వార్తతో మీ ముందుకు వచ్చాను. టెక్ ప్రపంచంలో ఇప్పుడు ఇదే హాట్ టాపిక్! Deno.. మన మోడరన్, సెక్యూర్ జావాస్క్రిప్ట్ అండ్ టైప్‌స్క్రిప్ట్ రన్‌టైమ్.. ఇప్పుడు Cloudflare లో భాగం కాబోతోంది. ఇది నిజంగా సంచలనం! Deno అంటే తెలుసు కదా? Node.js కి ఒక బెటర్ ఆల్టర్నేటివ్ గా వచ్చి, సెక్యూరిటీకి, పర్ఫార్మెన్స్ కి పెట్టింది పేరు. ఇక Cloudflare గురించి చెప్పనక్కర్లేదు. ప్రపంచవ్యాప్తంగా వెబ్ సైట్స్ కి స్పీడ్, సెక్యూరిటీ, ఇంకా వారి Serverless Workers తో డెవలపర్లకి ఎన్నో అవకాశాలు అందిస్తోంది. ఇప్పుడు ఈ రెండు పవర్ హౌజ్‌లు ఒక్కటవడం వల్ల డెవలపర్లకి, వెబ్ అప్లికేషన్లకి కొత్త శకం మొదలైనట్టే. ఎడ్జ్ కంప్యూటింగ్, సర్వర్లెస్ డెప్లాయ్‌మెంట్స్ మరింత వేగంగా, సురక్షితంగా మారబోతున్నాయి. Deno తన ఫీచర్స్ తో, Cloudflare తన గ్లోబల్ నెట్వర్క్ తో కలిసి పనిచేస్తే, భవిష్యత్తు వెబ్ అప్లికేషన్లు వేరే లెవెల్‌లో ఉంటాయి. మరి ఈ డెవలప్‌మెంట్ పై మీ అభిప్రాయం ఏంటి? కామెంట్స్ లో తెలియజేయండి. ఇలాంటి మరిన్ని టెక్ న్యూస్ కోసం మన ఛానెల్‌ను సబ్‌స్క్రైబ్ చేసుకోండి! జై హింద్!</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>tech, telugu, deno, cloudflare, javascript, webdevelopment, serverless, edgecomputing, techshorts, newsupdates</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,28 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-10 14:11:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OMG! డెన్మార్క్ డేటా లీక్ - పాస్‌వర్డ్ 123456! 😱 #TechNewsTelugu #CyberSecurity</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>హాయ్ టెక్ ఫ్యాన్స్! డెన్మార్క్ నుండి వచ్చిన ఈ వార్త మిమ్మల్ని షాక్ చేస్తుంది. ఆ దేశంలోని పౌరుల కీలక డేటాబేస్, CPR సిస్టమ్ లో భారీ డేటా చోరీ జరిగింది. అయితే, హ్యాకర్లు వాడిన పాస్‌వర్డ్ ఏంటో తెలుసా? '123456'! అవును, నిజం! ఇంత సున్నితమైన సమాచారం ఉన్న చోట, ఇంత బలహీనమైన పాస్‌వర్డ్ వాడటం నిజంగా ఆశ్చర్యకరం. దీని వల్ల లక్షలాది మంది డెన్మార్క్ ప్రజల వ్యక్తిగత వివరాలు ప్రమాదంలో పడ్డాయి. ఇది కేవలం వాళ్ళ సమస్య కాదు, మనందరికీ ఒక హెచ్చరిక! మీ ఆన్‌లైన్ భద్రత చాలా ముఖ్యం. బలమైన, ప్రత్యేకమైన పాస్‌వర్డ్‌లు వాడండి. టూ-ఫాక్టర్ అథెంటికేషన్ ఎనేబుల్ చేసుకోండి. సైబర్ దాడుల నుండి మిమ్మల్ని మీరు రక్షించుకోండి. ఈ వార్త గురించి మీరు ఏమనుకుంటున్నారో కామెంట్స్ లో చెప్పండి. మరిన్ని టెక్ అప్డేట్స్ కోసం మన ఛానెల్‌ని ఇప్పుడే సబ్‌స్క్రైబ్ చేసుకోండి!</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, cybersecurity, databreach, passwords, onlineprivacy, denmark</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,28 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-11 08:39:22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>యాండెక్స్ క్లౌడ్ డౌన్: మూడో డేటా సెంటర్ పై దాడి! 😱 #YandexCloud #TechNewsTelugu</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>నమస్కారం! టెక్ న్యూస్ షార్ట్స్ కి స్వాగతం! ఈరోజు టెక్ ప్రపంచం నుండి ఒక షాకింగ్ న్యూస్ తో వచ్చాను. ప్రముఖ క్లౌడ్ సర్వీస్ ప్రొవైడర్ Yandex Cloud తన మూడవ డేటా సెంటర్ లో పెద్ద సమస్యను ఎదుర్కొంది. ఇది సింపుల్ బగ్ కాదు, సర్వీసులకు అంతరాయం కలిగించే ఒక మేజర్ ఇన్సిడెంట్. దీనివల్ల చాలా వెబ్‌సైట్లు, ఆన్‌లైన్ సేవలు తీవ్రంగా ప్రభావితమయ్యే అవకాశం ఉంది. క్లౌడ్ సర్వీసులు మన డిజిటల్ లైఫ్ లో ఎంత కీలకమో మనందరికీ తెలుసు. ఇలాంటి అంతరాయాలు చిన్న స్టార్టప్‌ల నుండి పెద్ద కార్పొరేషన్ల వరకు అందరినీ ఇబ్బంది పెడతాయి. Yandex టీమ్ సమస్యను పరిష్కరించడానికి తీవ్రంగా కృషి చేస్తోంది. కానీ, ఈ ఘటన క్లౌడ్ భద్రత, స్థిరత్వం గురించి మరోసారి ప్రశ్నలు లేవనెత్తుతోంది. మీరు Yandex Cloud వాడుతున్నారా? లేదా ఇతర క్లౌడ్ సర్వీసులు వాడుతున్నారా? మీ అభిప్రాయాలను కామెంట్స్ లో తెలియజేయండి. మరిన్ని టెక్ న్యూస్ అప్డేట్స్ కోసం సబ్స్క్రైబ్ చేయడం మర్చిపోకండి! మళ్ళీ కలుద్దాం!</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, yandexcloud, datacenter, cloudoutage, cybersecurity, techupdates</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,31 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-11 08:57:13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Yandex Cloud కి భారీ దెబ్బ! 3వ డేటా సెంటర్ డౌన్! 😱 #YandexCloud #TechNewsTelugu</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>హే టెక్ ఫ్యాన్స్, వెల్కమ్ బ్యాక్! ఈరోజు ఒక బిగ్ బ్రేకింగ్ న్యూస్ తో మీ ముందుకు వచ్చాను. ప్రముఖ Yandex Cloud కు షాకింగ్ న్యూస్! వారి మూడవ డేటా సెంటర్ లో భారీ సంఘటన జరిగింది. దీనివల్ల చాలా క్లౌడ్ సర్వీసెస్ ప్రభావితమయ్యాయి.
+ఊహించని ఈ సంఘటన క్లౌడ్ సర్వీసెస్ భద్రత, విశ్వసనీయతపై తీవ్ర ప్రశ్నలు లేవనెత్తుతోంది. ఒక డేటా సెంటర్ దెబ్బతినడం అంటే అప్లికేషన్లు, వెబ్‌సైట్లు, కీలక డేటాకు అంతరాయం. యూజర్లు సర్వీసులు వాడుకోవడంలో ఇబ్బందులు పడ్డారు.
+ఇది సైబర్ దాడినా, లేక టెక్నికల్ ఫెయిల్యూరా, ఇంకా పూర్తి వివరాలు తెలియలేదు. కానీ ఇలాంటి సంఘటనలు భవిష్యత్తులోనూ జరగవచ్చని గుర్తు చేస్తున్నాయి. క్లౌడ్ కంపెనీలు మరింత కట్టుదిట్టమైన బ్యాకప్ మరియు భద్రతా చర్యలు తీసుకోవాలి.
+మీరు Yandex Cloud యూజర్లా? మీ సేవలు ఏమైనా ప్రభావితం అయ్యాయా? కింద కామెంట్స్ లో చెప్పండి. టెక్ అప్డేట్స్ కోసం ఛానెల్ ని ఫాలో అవ్వండి! మళ్ళీ కలుద్దాం!</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,6 +828,33 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:35:38</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>README ఫాలో అవ్వమని డబ్బులిచ్చారు! 🤯 Tech World Mystery!</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>హాయ్ టెక్ ఫ్యాన్స్! మీరు ఎప్పుడైనా ఒక సాఫ్ట్‌వేర్ ప్రాజెక్ట్ README ఫైల్ ఫాలో అవ్వడానికి కష్టపడ్డారా? చాలామందికి ఈ అనుభవం ఉంటుంది. కానీ ఒక డెవలపర్ దీనిపై ఒక ఆసక్తికరమైన ఎక్స్‌పెరిమెంట్ చేశాడు!
+అతను తన ప్రాజెక్ట్ README ని ఫాలో అయ్యి దాన్ని సెటప్ చేయమని కొంతమందికి డబ్బులు ఇచ్చాడు! వినడానికి వింతగా ఉంది కదా? అతను తన డాక్యుమెంటేషన్ ఎంత క్లియర్‌గా ఉందో తెలుసుకోవడానికి ఈ టెస్ట్ పెట్టాడు.
+కానీ చివరికి ఏం జరిగిందో తెలుసా? డబ్బులు ఇచ్చినప్పటికీ, చాలామంది ఆ README ని కరెక్ట్‌గా ఫాలో అవ్వలేకపోయారు! ఇది నిజంగా ఆశ్చర్యపరిచే విషయం.
+దీనితో ఒక విషయం స్పష్టమైంది. మనం ఒక ప్రాజెక్ట్‌కు డాక్యుమెంటేషన్ రాసేటప్పుడు అది ఎంత వివరంగా, స్పష్టంగా ఉండాలో! లేకపోతే యూజర్స్ చాలా కష్టపడతారు.
+సో, మీరు ఒక కొత్త ప్రాజెక్ట్ స్టార్ట్ చేసినప్పుడు, ఒక మంచి README ఎంత అవసరమో కదా? ఇది డెవలపర్‌ల టైమ్ ని కూడా చాలా సేవ్ చేస్తుంది.
+మీరు అలాంటి కష్టమైన READMEలను ఎప్పుడైనా చూశారా? లేదా మీరు రాసిన READMEని ఎవరైనా తప్పుగా ఫాలో అయ్యారా? మీ అనుభవాలను కామెంట్స్ లో షేర్ చేసుకోండి! ఈ షార్ట్ నచ్చితే లైక్ చేసి సబ్స్క్రైబ్ చేయండి!</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>tech, telugu, news, shorts, programming, developer, readme, documentation, coding, software</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,6 +855,32 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:18:50</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GLM-Legal: న్యాయవ్యవస్థలో AI విప్లవం! 🚀 #TechNewsTelugu #AILaw</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>హాయ్ టెక్ లవర్స్! AI ప్రతీ రంగాన్ని ఎలా మారుస్తుందో చూస్తున్నాం కదా? ఇప్పుడు న్యాయవ్యవస్థ వంతు వచ్చింది! 'GLM-Legal' అనే సరికొత్త AI గురించి తెలుసా?
+ఇది మామూలు AI కాదు, 'ఏజెంటిక్ లీగల్ ఇంటెలిజెన్స్'ని ముందుకు తీసుకెళ్తోంది. అంటే, న్యాయవాదులకు కేవలం సమాచారం ఇవ్వడమే కాదు, క్లిష్టమైన లీగల్ పనులను స్వయంగా విశ్లేషించి, పరిష్కారాలు సూచిస్తుంది!
+లీగల్ రీసెర్చ్, కేస్ అనాలసిస్, డాక్యుమెంట్ ప్రిపరేషన్... ఇలా ఎన్నో పనులను ఈ GLM-Legal చాలా వేగంగా, కచ్చితత్వంతో పూర్తి చేస్తుంది.
+దీనివల్ల న్యాయవాదుల సమయం ఆదా అవుతుంది, క్లయింట్‌లకు మెరుగైన సేవలు అందుతాయి. న్యాయరంగం మరింత సమర్థవంతంగా మారుతుంది.
+భవిష్యత్తులో న్యాయవాదుల పనితీరును GLM-Legal పూర్తిగా మార్చేస్తుంది అనడంలో సందేహం లేదు! ఈ డెవలప్‌మెంట్ గురించి మీరేమనుకుంటున్నారు? కామెంట్స్ లో చెప్పండి!</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, GLMLegal, law, legaltech, artificialintelligence</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,6 +881,28 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:31:42</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Apple HomeView: మీ ఇంటికి సరికొత్త స్మార్ట్ ఫీచర్! 🏠💡 #Apple #HomeView #SmartHome #TeluguTech</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>హే టెక్ లవర్స్! యాపిల్ నుండి మరో విప్లవాత్మక ఆవిష్కరణ వచ్చింది. అదే Apple HomeView! ఇది మీ ఇంటిని నియంత్రించడంలో కొత్త శకానికి నాంది పలకనుంది. HomeView తో, మీరు మీ స్మార్ట్ హోమ్ డివైజెస్‌ను ఒకే చోట నుండి సులువుగా మానిటర్ చేయొచ్చు, కంట్రోల్ చేయొచ్చు. లైట్స్ ఆన్ చేయడమా? డోర్ లాక్ చేయడమా? టెంపరేచర్ అడ్జస్ట్ చేయడమా? అన్నీ మీ చేతివేళ్ల వద్దే! ఇది కేవలం సౌకర్యమే కాదు, మీ ఇంటి భద్రతను కూడా నెక్స్ట్ లెవెల్‌కి తీసుకెళ్తుంది. అధునాతన సెక్యూరిటీ ఫీచర్లు, ప్రైవసీకి పెద్ద పీట వేస్తూ, యాపిల్ మీకు సంపూర్ణ మనశ్శాంతిని అందిస్తుంది. మీ ఇంటిని స్మార్ట్‌గా, సురక్షితంగా మార్చాలనుకుంటున్నారా? యాపిల్ HomeView ని తప్పకుండా చూడండి! మరిన్ని టెక్ అప్‌డేట్స్ కోసం ఫాలో అవ్వండి!</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>tech, telugu, apple, homeview, smarthome, innovation, news, shorts, iot, homeautomation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,6 +903,31 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:16:41</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Iosevka Font: డెవలపర్స్ కోసం పర్ఫెక్ట్ ఫాంట్! #TechNewsTelugu #Iosevka #Font</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>హాయ్ టెక్ ప్రియులారా! ఈరోజు ఒక అదిరిపోయే న్యూస్ తో మీ ముందుకొచ్చాను. డెవలపర్స్, డిజైనర్స్ అందరూ ఎదురుచూస్తున్న Iosevka ఫాంట్ గురించి తెలుసా? ఇది కేవలం ఒక ఫాంట్ కాదు, మీ కోడింగ్, టైపింగ్ అనుభవాన్ని మార్చేసే అద్భుతమైన టూల్!
+Iosevka అనేది ఒక ఓపెన్-సోర్స్, మోనోస్పేస్ ఫాంట్. అంటే అక్షరాలు అన్నీ ఒకే వెడల్పులో ఉంటాయి, ఇది కోడ్ చదవడానికి చాలా సులువుగా చేస్తుంది. అంతేకాదు, ఇది శాన్-సెరిఫ్ మరియు స్లాబ్-సెరిఫ్ స్టైల్స్ రెండింటినీ అందిస్తుంది, కాబట్టి మీ ప్రాజెక్ట్‌కి తగ్గట్టుగా ఎంచుకోవచ్చు.
+మీరు డెవలపర్ అయినా, కంటెంట్ క్రియేటర్ అయినా, లేదా ఎవరైనా సరే, స్పష్టమైన, చదవగలిగే ఫాంట్ కోసం చూస్తున్నట్లయితే, Iosevka మీకు బెస్ట్ ఛాయిస్. దీని డిజైన్ చాలా క్లీన్ గా ఉంటుంది, కళ్ళకు ఎటువంటి స్ట్రెయిన్ లేకుండా గంటల తరబడి పని చేయొచ్చు.
+మరి ఈ ఓపెన్-సోర్స్ Iosevka ఫాంట్‌ని మీ సిస్టమ్‌లో ఇప్పుడే ట్రై చేయండి. మీ టెక్ వర్క్ ఫ్లోలో ఎంత మార్పు వస్తుందో మీరే చూడండి! టెక్ అప్‌డేట్స్ కోసం మా ఛానెల్‌ని సబ్‌స్క్రైబ్ చేయడం మర్చిపోవద్దు!</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>tech, telugu, news, shorts, font, programming, coding, opensource, developers, design, typography</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,6 +928,28 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:59:23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>కోడింగ్ లో కొత్త ట్రిక్! | Functions Without Parentheses #TechNews #TeluguTech #CodingHacks</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>హే టెక్ ప్రియులారా! కోడింగ్‌లో ఎప్పుడూ ఫంక్షన్స్‌ని కాల్ చేయడానికి బ్రాకెట్‌లు వాడతాం కదా? ఇప్పుడు ఆ బ్రాకెట్‌లు లేకుండానే ఫంక్షన్స్‌ని ఇన్వోక్ చేసే సరికొత్త పద్ధతి ఒకటి వచ్చేసింది! ఇది డెవలపర్‌లకి చాలా టైం సేవ్ చేస్తుందట. కోడ్‌ని మరింత క్లీన్‌గా, ఈజీగా చదవగలిగేలా చేస్తుందని అంటున్నారు. సాధారణంగా ఫంక్షన్ కాల్స్ అంటే ఒక పద్ధతి. కానీ ఈ కొత్త అప్రోచ్ ప్రోగ్రామింగ్ వరల్డ్‌లో ఒక చిన్న విప్లవం లాంటిది. దీని వల్ల కోడింగ్ ప్రాసెస్‌ మరింత సింప్లిఫై అవుతుంది, అంతేకాదు, ఎర్రర్స్ కూడా తగ్గుతాయని అంచనా వేస్తున్నారు. ఈ వినూత్నమైన టెక్నిక్ గురించి మీరు ఏమనుకుంటున్నారు? డెవలపర్‌లకి ఇది నిజంగా ఉపయోగపడుతుందా? మీ అభిప్రాయాలను కామెంట్స్ లో పంచుకోండి! మరిన్ని టెక్ అప్‌డేట్స్ కోసం సబ్స్క్రైబ్ చేయడం మర్చిపోవద్దు!</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, coding, programming, developers, innovation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,6 +950,32 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:57:23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DeepSeek v4.1 Flash 1017: AI లో కొత్త సంచలనం! ⚡️ #DeepSeek #AITech #TeluguTech</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>నమస్తే! మీ Tech Updates ఛానెల్‌కి స్వాగతం! AI ప్రపంచంలోకి ఒక కొత్త శక్తి వచ్చింది – అదే DeepSeek v4.1 Flash 1017!
+ఇది కేవలం ఒక అప్‌డేట్ కాదు, AI మోడల్స్‌లో ఒక పెద్ద సంచలనం! 'Flash' అంటేనే అర్థం చేసుకోవచ్చు – ఇది చాలా వేగంగా, మరింత సమర్ధవంతంగా పనిచేస్తుంది.
+మునుపటి వెర్షన్ల కంటే ఇది మెరుగైన పెర్ఫార్మెన్స్, మరింత ఖచ్చితమైన సమాచారం, ఇంకా వేగవంతమైన ప్రాసెసింగ్‌తో దూసుకుపోతోంది. డెవలపర్‌లకి, బిజినెస్‌లకి ఇది ఒక కొత్త టూల్.
+కాంప్లెక్స్ టాస్క్‌లను కూడా సులువుగా, స్పీడ్‌గా పూర్తి చేయగల సామర్థ్యం దీని సొంతం. DeepSeek v4.1 Flash తో AI అప్లికేషన్లు మరింత స్మార్ట్‌గా, యూజర్ ఫ్రెండ్లీగా మారబోతున్నాయి!
+మీరు ఈ కొత్త AI మోడల్ గురించి ఏమనుకుంటున్నారు? ఇది మీ పనికి ఎలా ఉపయోగపడుతుంది? కామెంట్లలో తెలియజేయండి! మరిన్ని ఆసక్తికరమైన Tech Updates కోసం మా ఛానెల్‌ని సబ్‌స్క్రైబ్ చేసుకోండి!</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, deepseek, artificialintelligence, techupdates, ai_model, flash1017, technews</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,6 +976,28 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-18 12:25:32</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DeepSeek AI Cost Revolution! | డీప్‌సీక్ AI ధరలు తగ్గించింది! #TechNews #AIShorts</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>హేయ్ టెక్ ప్రియులారా! మీరందరూ ఎదురుచూస్తున్న లేటెస్ట్ టెక్ న్యూస్ తో నేను మీ ముందుకు వచ్చేశాను! ఈరోజు మనం డీప్‌సీక్ గురించి మాట్లాడుకుందాం. DeepSeek వారి 'సెర్చ్ అండ్ ఫెచ్' సర్వీస్‌కి అద్భుతమైన కొత్త ధరను ప్రకటించింది – కేవలం $0.75కు 1000 సక్సెస్ఫుల్ రిక్వెస్ట్‌లు! అవును, మీరు విన్నది నిజం! ఇది డెవలపర్‌లకు, AI అప్లికేషన్‌లకు ఎంతగానో ఉపయోగపడనుంది. డేటాను సేకరించడం, సమాచారం వెతకడం ఇప్పుడు మరింత సులభం, చవకగా మారిపోతుంది. కేవలం 75 సెంట్లు అంటే దాదాపు 60 రూపాయలకే 1000 విజయవంతమైన రిక్వెస్ట్‌లు పొందొచ్చు. ఇది చిన్న స్టార్టప్‌ల నుండి పెద్ద కంపెనీల వరకు అందరికీ అందుబాటులోకి తెస్తుంది. ఈ కొత్త ధరల గురించి మీరేమనుకుంటున్నారు? కామెంట్స్‌లో చెప్పండి. ఇలాంటి మరిన్ని టెక్ అప్‌డేట్స్ కోసం మన ఛానెల్‌ని సబ్‌స్క్రైబ్ చేసుకోండి! స్టే ట్యూన్డ్!</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, deepseek, artificialintelligence, developer, costeffective</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -998,6 +998,32 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:15:14</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DeepSeek's AI Revolution: Inference Engine Now Open Source! #TeluguTech #AI</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>హే, తెలుగు టెక్ లవర్స్! బిగ్ బ్రేకింగ్ న్యూస్! DeepSeek ఇప్పుడు తన శక్తివంతమైన AI ఇన్ఫరెన్స్ ఇంజిన్‌ను ఓపెన్ సోర్స్ చేసేసింది! అంటే ఏంటి? దీనివల్ల AI ప్రపంచంలో ఏం మార్పు రాబోతుంది? తెలుసుకుందాం!
+సాధారణంగా AI మోడల్స్ ని రన్ చేయడానికి చాలా కష్టం, ఖర్చు కూడా ఎక్కువ. కానీ DeepSeek తన DeepInfer ఇంజిన్‌ను ఓపెన్ సోర్స్ చేయడం ద్వారా, AI మోడల్స్ ఇప్పుడు మరింత వేగంగా, సమర్థవంతంగా పనిచేస్తాయి. ఇది డెవలపర్‌లకు, స్టార్టప్‌లకు నిజంగా గేమ్ ఛేంజర్!
+ఇకపై చిన్న కంపెనీలు కూడా పెద్ద AI మోడల్స్‌ను తక్కువ ఖర్చుతో, సులువుగా వాడుకోవచ్చు. AI టెక్నాలజీ మరింత మందికి అందుబాటులోకి వస్తుంది. ఇది AI డెవలప్‌మెంట్‌ను డెమోక్రాటైజ్ చేస్తుంది.
+వేగవంతమైన AI, తక్కువ ఖర్చుతో కూడుకున్న పరిష్కారాలు, మరిన్ని సరికొత్త ఆవిష్కరణలు! భవిష్యత్తులో మనం చూడబోయే అద్భుతమైన AI అప్లికేషన్స్‌కు ఇది ఒక బలమైన పునాది. DeepSeek కు హ్యాట్సాఫ్!
+ఈ టెక్ అప్‌డేట్ మీకు నచ్చిందా? అయితే లైక్ చేయండి, మరిన్ని అప్డేట్స్ కోసం సబ్స్క్రైబ్ చేసుకోండి!</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, deepseek, opensource, artificialintelligence, deepinfer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,6 +1024,28 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:23:23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>షాకింగ్: డచ్ సైబర్ సెక్యూరిటీ సెంటర్ PHP వల్ల డౌన్! | NCSC Offline Due to PHP!</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>హే టెక్ లవర్స్, అదిరిపోయే వార్త ఒకటి మీకోసం! నెదర్లాండ్స్ నేషనల్ సైబర్ సెక్యూరిటీ సెంటర్ (NCSC) అకస్మాత్తుగా ఆఫ్ లైన్ అయింది. ప్రపంచంలోనే అత్యున్నత సైబర్ భద్రతా సంస్థల్లో ఒకటి, ఎంతో కీలకమైనది, కానీ ఎందుకో తెలుసా? వాళ్ళు వాడే PHP ప్రోగ్రామింగ్ లాంగ్వేజ్ లోని కొన్ని సమస్యల వల్ల! అవును, PHP వల్ల ఒక దేశ సైబర్ డిఫెన్స్ సెంటర్ కూలిపోయింది. ఇది పాత టెక్నాలజీ అప్‌డేట్ చేయకపోతే వచ్చే రిస్కులకు ఒక పెద్ద ఉదాహరణ. సైబర్ భద్రతకే భద్రత లేకపోతే ఎలా? సో, టెక్ అప్‌డేట్స్ చాలా ముఖ్యం! ఇలాంటి ఆసక్తికరమైన టెక్ న్యూస్ కోసం మా ఛానెల్‌ని ఇప్పుడే సబ్స్క్రైబ్ చేసుకోండి!</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>tech, telugu, cybersecurity, news, shorts, php, ncsc, technology, digitalindia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,6 +1046,31 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:24:10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ఆన్‌లైన్ డేటా ప్రమాదంలో! ⚠️ CVE-2026-111943 Explained! #TechNewsTelugu #CyberSecurity</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>హే గాయ్స్, లేటెస్ట్ టెక్ న్యూస్ తో మీ ముందుకు వచ్చేసా! ఈ రోజు ఆన్లైన్ ప్రపంచంలో ఓ పెద్ద ప్రమాదం గురించి తెలుసుకుందాం. CVE-2026-111943. వినడానికి ఏదో కోడ్ లా ఉంది కదా? కానీ ఇది చాలా డేంజరస్ వార్త. ఒక Intermediate Certificate Authority కాంప్రమైజ్ అయ్యింది!
+అసలు ఈ Certificate Authority అంటే ఏంటి? సింపుల్ గా చెప్పాలంటే, మనం వెబ్సైట్లు విజిట్ చేసినప్పుడు, అది నిజమైనదేనా, సేఫ్ గా ఉందా అని ధృవీకరించే సంస్థ ఇది. మీ బ్రౌజర్ లో పైన లాక్ సింబల్ చూస్తారు కదా, అది ఈ సర్టిఫికేట్ వల్లనే వస్తుంది.
+ఇప్పుడు, ఈ Intermediate CA ప్రైవేట్ కీస్ హ్యాకర్ల చేతికి చిక్కాయి. దీని అర్థం ఏంటంటే, హ్యాకర్లు నకిలీ వెబ్సైట్లకు కూడా నిజమైన, సేఫ్ సర్టిఫికేట్లను ఇవ్వగలరు! మీరు ఒక ఫేక్ బ్యాంకింగ్ సైట్ లోకి వెళ్లి, అది సేఫ్ అని భావించి మీ లాగిన్ వివరాలు ఇచ్చే ప్రమాదం ఉంది. మీ పర్సనల్ డేటా, బ్యాంక్ డీటెయిల్స్ అన్నీ డేంజర్ లో పడతాయి.
+ఇది సైబర్ సెక్యూరిటీ చరిత్రలో ఓ కీలకమైన సంఘటన. మరి మనం ఏం చేయాలి? ఎప్పుడూ మీ బ్రౌజర్ ను, ఆపరేటింగ్ సిస్టమ్ ను లేటెస్ట్ వెర్షన్ కు అప్డేట్ చేసుకోండి. అనుమానాస్పద లింకులను క్లిక్ చేయకండి. మీ ఆన్లైన్ సేఫ్టీ మీ చేతుల్లోనే! టెక్ అప్డేట్స్ కోసం మన ఛానల్ ని ఫాలో అవ్వండి!</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>tech, telugu, news, shorts, cybersecurity, cve, dataprotection, onlinesafety, hack, certificateauthority</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1071,6 +1071,28 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:02:25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Local Wikipedia: మీ చుట్టూ ఉన్న ప్రపంచం! 🚶‍♂️🌍 #TechTelugu #LocalWiki</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>హాయ్ టెక్ ప్రియులారా! మీ కోసం ఒక అదిరిపోయే వార్త! వికీపీడియా గురించి మనందరికీ తెలుసు కదా? అయితే ఇప్పుడు 'లోకల్ వికీపీడియా' అనే కొత్త కాన్సెప్ట్ వచ్చింది! ఇది ఏమిటంటే... మీ చుట్టూ, సరిగ్గా అరగంట నడిచి వెళ్ళే దూరంలో ఉన్న విషయాల గురించే సమాచారం ఇస్తుంది! అంటే, మీ ఏరియాలో ఉన్న చారిత్రక ప్రదేశాలు, దాగి ఉన్న రెస్టారెంట్లు, స్థానిక సంఘటనలు... అన్నింటి గురించి తెలుసుకోవచ్చు! ఇది స్థానిక కమ్యూనిటీలు తమ పరిసరాల గురించి సమాచారం పంచుకోవడానికి గొప్ప వేదిక. మీరే కంటెంట్ క్రియేట్ చేయొచ్చు! మీ చుట్టూ ఉన్న ప్రపంచాన్ని కొత్త కోణంలో చూసేందుకు సిద్ధంగా ఉన్నారా? 'లోకల్ వికీపీడియా'తో మీ లోకల్ ఎక్స్‌ప్లోరేషన్‌కి శ్రీకారం చుట్టండి! ఎంత బాగుందో కదా? డోంట్ మిస్ ఇట్!</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>tech, telugu, news, shorts, localwiki, community, exploration, తెలుగుటెక్, ఆవిష్కరణ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,6 +1093,28 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:26:21</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>క్వాంటమ్ ఫిజిక్స్ అర్థం కావడం లేదు?! 🤯 టెక్ సైంటిస్టుల షాకింగ్ నిజం! #QuantumPhysics #TechTelugu #Shorts</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>హాయ్ టెక్ ఫ్యాన్స్! కొన్ని టెక్ కాన్సెప్ట్స్ మీకు అర్థం కావట్లేదా? కొన్నిసార్లు మనం అర్థం చేసుకోవడానికి చాలా కష్టపడతాం కదా? అయితే, 2018లో వచ్చిన ఈ షాకింగ్ న్యూస్ చూడండి! ఒక ప్రముఖ శాస్త్రవేత్త స్వయంగా 'నాకు క్వాంటమ్ ఫిజిక్స్ అర్థం కాలేదు' అని చెప్పారట! వినడానికి వింతగా ఉన్నా, ఇది నిజం. క్వాంటమ్ ఫిజిక్స్ ఎంత సంక్లిష్టమైనదో, ఎంత అంతుచిక్కనిదో చెప్పడానికి ఇదే పెద్ద ఉదాహరణ. మన ఊహకు అందదు, ఎంతో మంది దిగ్గజ ప్రొఫెసర్లకే పూర్తిగా అర్థం కాదు! అయినా సరే, క్వాంటమ్ కంప్యూటింగ్, AI, కొత్త జనరేషన్ టెక్నాలజీలకు ఇదే ఆధారం. భవిష్యత్ టెక్నాలజీ అంతా దీని పైనే ఆధారపడి ఉంది! మరి, మీరు క్వాంటమ్ ఫిజిక్స్ గురించి ఏమనుకుంటున్నారు? ఇది మీకు అర్థం అవుతుందా? కామెంట్స్ లో మీ అభిప్రాయం చెప్పండి! స్టే ట్యూన్డ్ ఫర్ మోర్ టెక్ అప్డేట్స్!</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, quantumphysics, quantumcomputing, science, physics, techfacts</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1115,6 +1115,28 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:15:23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>vLLMలో AI టూల్స్ ఇప్పుడు మరింత కచ్చితమైనవి! 🚀 #AITech #vLLM #TeluguTech</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>హేయ్ టెక్ ప్రియులారా! AI ప్రపంచంలో vLLM ఎంత ఫాస్ట్ అన్నది అందరికీ తెలుసు. భారీ లాంగ్వేజ్ మోడల్స్‌ని వేగంగా రన్ చేయడానికి ఇదొక అద్భుతమైన ఇంజిన్! అయితే, ఇందులో ఒక ముఖ్యమైన ఛాలెంజ్ ఉంది - 'టూల్-కాల్ అక్యూరసీ'. అంటే, ఒక AI మోడల్ బయట టూల్స్, APIs ని వాడాల్సి వచ్చినప్పుడు, సరైన టూల్‌ని, సరైన పద్ధతిలో కాల్ చేయడంలో కొన్నిసార్లు తప్పులు జరుగుతున్నాయి. ఇది AI ఇచ్చే ఫలితాలను ప్రభావితం చేస్తుంది! కానీ, డెవలపర్లు ఇప్పుడు ఈ సమస్యను పరిష్కరించడానికి ఒక అద్భుతమైన మార్గాన్ని కనుగొన్నారు. vLLMలో టూల్-కాలింగ్ మెకానిజంను మెరుగుపరచడం ద్వారా, AI ఎప్పుడూ సరైన నిర్ణయాలు తీసుకునేలా, కచ్చితమైన అవుట్‌పుట్‌ని ఇచ్చేలా చేస్తున్నారు. ఇది AI అప్లికేషన్స్‌లో విశ్వసనీయతను పెంచుతుంది. ఇకపై మీ AI అసిస్టెంట్ ఎప్పుడూ తప్పు చేయదు! AI మరింత స్మార్ట్‌గా, కచ్చితంగా పనిచేయడానికి ఇది చాలా పెద్ద అప్డేట్. మీ అభిప్రాయాలు కామెంట్స్‌లో పంచుకోండి, మరిన్ని టెక్ అప్‌డేట్స్ కోసం ఫాలో అవ్వండి!</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, vllm, llm, artificialintelligence, toolcalling</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1137,6 +1137,32 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:53:44</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>సైన్స్‌లో 3 సంచలన ఆవిష్కరణలు! | AIతో కొత్త యుగం! #TechNewsTelugu #AI</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>హాయ్ టెక్ ఫ్యాన్స్! ఈరోజు సైన్స్ ప్రపంచంలో ఒక సంచలన వార్తతో మీ ముందుకు వచ్చాను! OpenAI నుండి వచ్చిన అప్డేట్ ప్రకారం, గణితం, కంప్యూటర్ సైన్స్, ఇంకా ఫిజిక్స్... ఈ మూడు కీలక రంగాలలో సరికొత్త ఆవిష్కరణలు జరిగాయి.
+గణితంలో సంక్లిష్ట సమస్యలకు సులభమైన, కొత్త పరిష్కారాలు దొరికాయి. ఇది డేటా అనాలిసిస్, కృత్రిమ మేధస్సు అభివృద్ధికి ఎంతో సహాయపడుతుంది.
+కంప్యూటర్ సైన్స్‌లో వచ్చిన ఈ అడ్వాన్స్‌మెంట్, మనం టెక్నాలజీతో ఇంటరాక్ట్ అయ్యే విధానాన్ని పూర్తిగా మార్చేస్తుంది. ఇది AI సామర్థ్యాలను మరింత పెంచుతుంది.
+ఇక ఫిజిక్స్ విషయానికి వస్తే, మన విశ్వం, క్వాంటం ప్రపంచం గురించి కొత్త సిద్ధాంతాలు వెలుగులోకి వచ్చాయి. ఇవి భవిష్యత్ టెక్నాలజీలకు పునాది వేస్తాయి.
+ఈ మూడు ఆవిష్కరణలు కేవలం శాస్త్రవేత్తలకే కాదు, మనందరి భవిష్యత్తుకు చాలా కీలకం. AI పరిశోధనల వేగాన్ని ఎలా పెంచుతుందో స్పష్టంగా చూపిస్తోంది. మరిన్ని ఇంట్రెస్టింగ్ టెక్ న్యూస్ అప్‌డేట్స్ కోసం, మన ఛానెల్‌ని ఇప్పుడే సబ్‌స్క్రైబ్ చేసుకోండి!</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, science, discoveries, openai</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1163,6 +1163,28 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:48:26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MacBook యూజర్స్ కి బిగ్ షాక్! Git సెక్యూరిటీలో పెద్ద లోపం! #MacBook #Git #CybersecurityTelugu</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>హేయ్ టెక్ గీక్స్! మీరు మ్యాక్‌బుక్ యూజరా? ముఖ్యంగా Git డెవలపర్స్ అయితే, ఈ వార్త మీకోసం! షాకింగ్ న్యూస్ ఏంటంటే, పది రోజులు గడిచినా, macOS లోని Git ఇంకా కాంప్రమైజ్ అయిన eMudhra సర్టిఫికెట్స్ ని నమ్ముతోంది. అవును, మీరు విన్నది నిజం! ఈ eMudhra సర్టిఫికెట్స్ భద్రత ప్రశ్నార్థకం అయినప్పటికీ, Apple సిస్టమ్ ఇంకా వాటిని వాడుతోంది. దీనివల్ల మీ కోడ్, ప్రాజెక్ట్స్, మరియు డేటా సెక్యూరిటీకి రిస్క్ ఉందని నిపుణులు హెచ్చరిస్తున్నారు. ఈ సెక్యూరిటీ లోపం ఎందుకు పరిష్కరించబడట్లేదు అనేది పెద్ద ప్రశ్న. డెవలపర్స్, ఈ విషయంపై చాలా ఆందోళన చెందుతున్నారు. వెంటనే మీ సిస్టమ్ అప్డేట్స్ చెక్ చేసుకోండి, అవసరమైతే ఆ eMudhra సర్టిఫికెట్స్ ని మాన్యువల్ గా తీసేయండి. లేదంటే మీ డేటాకి ప్రమాదం ఉండొచ్చు! మరిన్ని టెక్ అప్డేట్స్ కోసం సబ్స్క్రైబ్ చేయడం మర్చిపోవద్దు!</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>tech, telugu, cybersecurity, macOS, git, emudhra, security, apple, developer, shorts</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,6 +1185,28 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:26:05</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MacOS users beware! Git Security Issue ⚠️ #MacOS #Git #eMudhra #TechNewsTelugu</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>హే టెక్ మిత్రులారా! షాకింగ్ న్యూస్ తో వచ్చేశా! MacOS యూజర్లారా, మీ Git సెక్యూరిటీ ప్రమాదంలో ఉందా? పది రోజులైనా, MacOS లో Git ఇంకా compromised eMudhra certificates ని ట్రస్ట్ చేస్తోందని తెలుస్తోంది! eMudhra అనేది మన డిజిటల్ ట్రస్ట్ కి సంబంధించినది. కానీ ఇప్పుడు వాటి సర్టిఫికెట్స్ లీక్ అయ్యాయి లేదా దుర్వినియోగం అవుతున్నాయి. ఇది చాలా సీరియస్ విషయం. దీనివల్ల మీ కమ్యూనికేషన్స్ అండ్ కోడ్ ని ఎవరైనా రహస్యంగా వినడానికి లేదా మార్చడానికి అవకాశం ఉంది. మ్యాన్‌-ఇన్-ది-మిడిల్ అటాక్స్ గురించి వినే ఉంటారు కదా? అలాంటి ప్రమాదం ఇప్పుడు Git యూజర్లకి పొంచి ఉంది. అదీ పది రోజులుగా ఈ సమస్య ఉన్నా కూడా ఇంకా పరిష్కరించబడలేదు. మీ సిస్టమ్స్ ని అప్డేట్ చేసుకోండి, మీ Git కాన్ఫిగరేషన్స్ ని చెక్ చేసుకోండి. తెలియని సర్టిఫికెట్స్ ని నమ్మకండి. ఈ సమస్యపై మరింత సమాచారం కోసం డిస్క్రిప్షన్ చూడండి. మీ డేటా సెక్యూరిటీ మీ చేతుల్లోనే! స్టే సేఫ్, స్టే టెక్!</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>tech, telugu, macos, git, emudhra, cybersecurity, news, shorts</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1207,6 +1207,28 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:54:39</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mistral Large 4 (Le Chonk) Is Open! AI వార్తలు! #TeluguTech #AI #MistralAI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>హాయ్ టెక్ ప్రియులారా! ఇదో సంచలన వార్త! ఆర్టిఫిషియల్ ఇంటెలిజెన్స్ ప్రపంచంలో ఒక సరికొత్త అధ్యాయం మొదలైంది! మీరు ఎదురుచూస్తున్న Mistral Large 4, దాని సరదా పేరు 'Le Chonk'తో, ఇప్పుడు అందరికీ అందుబాటులోకి వచ్చేసింది! ఇది 'ఓపెన్ వెయిట్'గా రిలీజ్ అయ్యింది అంటే, ఇక డెవలపర్లు, రీసెర్చర్లు ఈ శక్తివంతమైన AI మోడల్‌ను ఉచితంగా ఉపయోగించుకోవచ్చు, మార్పులు చేసుకోవచ్చు! అంటే ఇప్పుడు మీరు ఏ అప్లికేషన్‌కైనా, ఏ ప్రాజెక్ట్‌కైనా ఈ అడ్వాన్స్‌డ్ AIని ఇంటిగ్రేట్ చెయ్యొచ్చు. సరికొత్త ఆవిష్కరణలకు మార్గం సుగమం అయ్యింది. చిన్న స్టార్టప్‌ల నుండి పెద్ద కంపెనీల వరకు అందరికీ Mistral Large 4 అందుబాటులో ఉండడం AI భవిష్యత్తును మరింత ఉజ్వలం చేస్తుంది. మరిన్ని అద్భుతమైన టెక్ వార్తల కోసం మన ఛానెల్‌ను సబ్‌స్క్రైబ్ చేయడం మర్చిపోవద్దు! టెక్ ప్రపంచంలో సరికొత్త విశేషాలతో మళ్ళీ కలుద్దాం!</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1229,6 +1229,32 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:47:12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AI గుర్రాలను ఎన్నుకుంటుందా? | elect.horse Explained! #AIShorts #TeluguTech</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>టెక్ ప్రపంచంలో కొత్త సంచలనం! AI ఇప్పుడు గుర్రాలను కూడా ఎన్నుకుంటుందా? అవును, మీరు విన్నది నిజం!
+`elect.horse` అనే కొత్త ప్రాజెక్ట్ ఇప్పుడు హాట్ టాపిక్. ఒక గుర్రాన్ని ఎన్నుకునే ఈ వినూత్న ఆలోచన వెనుక ఉంది అధునాతన ఆర్టిఫిషియల్ ఇంటెలిజెన్స్!
+మెషిన్ లెర్నింగ్ అల్గోరిథమ్స్ ద్వారా, AI ఈ గుర్రపు ఎన్నికల ప్రచారాన్ని నడుపుతోంది. ఊహించని రంగాల్లో AI సామర్థ్యం ఎలా పెరుగుతుందో దీని ద్వారా మనం చూడొచ్చు.
+ఇది కేవలం ఒక సరదా ప్రాజెక్ట్ కాదు, భవిష్యత్తులో AI మన దైనందిన జీవితంలో ఎలా చొచ్చుకుపోతుందో చెప్పడానికి ఒక చిన్న ఉదాహరణ. టెక్నాలజీ సరిహద్దులు లేవని ఇది నిరూపిస్తోంది!
+మరి మీరు ఏ గుర్రాన్ని ఎన్నుకుంటారు? ఈ వింత టెక్ న్యూస్ గురించి మీ అభిప్రాయం ఏంటి? కామెంట్ చేయండి, మర్చిపోకుండా మన ఛానెల్‌ని సబ్‌స్క్రైబ్ చేసుకోండి!</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts, electhorse, machinelearning, innovation, futuretech, viraltech</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,6 +1255,32 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-31 14:14:33</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ప్రపంచంలోనే అత్యంత తెలివైన పార్లమెంట్! 🤯 #SerbiaTech #TeluguTechNews</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>హే, టెక్ లవర్స్! ఒక ఇంట్రెస్టింగ్ న్యూస్ తెలుసా? ప్రపంచంలోనే అత్యంత తెలివైన పార్లమెంట్ ఎక్కడ ఉందో తెలుసా? అది సెర్బియాలో! అవును, మీరు విన్నది నిజం!
+రీసెంట్‌గా సెర్బియాలో జరిగిన ఎన్నికల్లో, కొత్తగా ఎంపికైన ఎంపీలలో చాలామందికి PhDలు, ఉన్నత విద్య అర్హతలు ఉన్నాయట. అంటే, టెక్నాలజీ, సైన్స్, ఇంజనీరింగ్ బ్యాక్‌గ్రౌండ్ ఉన్నవాళ్ళు ఎక్కువ మంది రాజకీయాల్లోకి వచ్చారన్నమాట!
+సాధారణంగా రాజకీయాల్లో ఇలాంటి ఉన్నత విద్యావంతులు తక్కువగా ఉంటారు. కానీ సెర్బియాలో ఈ ట్రెండ్ రివర్స్ అయ్యింది. ఇది దేశ అభివృద్ధికి, ముఖ్యంగా టెక్నాలజీ మరియు ఇన్నోవేషన్ రంగాల్లో అద్భుతమైన మార్పులు తీసుకురాగలదని నిపుణులు అంటున్నారు.
+సమస్యలను సైంటిఫిక్ పద్ధతిలో విశ్లేషించడం, డేటా ఆధారిత నిర్ణయాలు తీసుకోవడం, భవిష్యత్తు కోసం సమర్థవంతమైన పాలసీలు రూపొందించడం వంటివి ఈ మేధావులు ఈజీగా చేయగలరు.
+సో, సెర్బియా టెక్నాలజీ హబ్‌గా మారడానికి ఇది మొదటి అడుగు కావచ్చు! ఈ డెవలప్‌మెంట్ గురించి మీరేమనుకుంటున్నారు? కామెంట్స్ లో చెప్పండి! మరిన్ని టెక్ అప్డేట్స్ కోసం ఫాలో అవ్వండి!</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>tech, telugu, ai, news, shorts</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
